--- a/research/traditional_assets/database/data/thailand/thailand_air_transport.xlsx
+++ b/research/traditional_assets/database/data/thailand/thailand_air_transport.xlsx
@@ -588,118 +588,115 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.282</v>
+        <v>-0.1985</v>
       </c>
       <c r="G2">
-        <v>-1.088082030593377</v>
+        <v>-0.4807651019810676</v>
       </c>
       <c r="H2">
-        <v>-1.088082030593377</v>
+        <v>-0.4807651019810676</v>
       </c>
       <c r="I2">
-        <v>-1.367969724323939</v>
+        <v>-0.625726693477907</v>
       </c>
       <c r="J2">
-        <v>-1.367969724323939</v>
+        <v>-0.625726693477907</v>
       </c>
       <c r="K2">
-        <v>-969.2</v>
+        <v>-691.2</v>
       </c>
       <c r="L2">
-        <v>-1.629181375021012</v>
+        <v>-0.674538889431053</v>
       </c>
       <c r="M2">
-        <v>80.7</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.00288507945587473</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.08326454808089145</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>80.7</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.00288507945587473</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>-0.08326454808089145</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>305.387</v>
+        <v>230.2</v>
       </c>
       <c r="V2">
-        <v>0.01091779132331123</v>
+        <v>0.006877677723136125</v>
       </c>
       <c r="W2">
-        <v>-0.2680649192453623</v>
+        <v>-0.1257537315252644</v>
       </c>
       <c r="X2">
-        <v>0.1161283177870938</v>
+        <v>0.1549375385253032</v>
       </c>
       <c r="Y2">
-        <v>-0.3841932370324561</v>
+        <v>-0.2806912700505676</v>
       </c>
       <c r="Z2">
-        <v>0.07514564969128183</v>
+        <v>0.1266496510389408</v>
       </c>
       <c r="AA2">
-        <v>-0.07939164499191241</v>
+        <v>-0.05835249036272007</v>
       </c>
       <c r="AB2">
-        <v>0.07077007948149781</v>
+        <v>0.1060562429226656</v>
       </c>
       <c r="AC2">
-        <v>-0.1493553101151446</v>
+        <v>-0.1658249454160807</v>
       </c>
       <c r="AD2">
-        <v>4445.1</v>
+        <v>4234.8</v>
       </c>
       <c r="AE2">
-        <v>61.42594500155693</v>
+        <v>76.6107140340563</v>
       </c>
       <c r="AF2">
-        <v>4506.525945001556</v>
+        <v>4311.410714034057</v>
       </c>
       <c r="AG2">
-        <v>4201.138945001557</v>
+        <v>4081.210714034057</v>
       </c>
       <c r="AH2">
-        <v>0.1387561532413617</v>
+        <v>0.1141127915786809</v>
       </c>
       <c r="AI2">
-        <v>0.5194946819190327</v>
+        <v>0.5558369335505532</v>
       </c>
       <c r="AJ2">
-        <v>0.1305811112412418</v>
+        <v>0.1086821284095578</v>
       </c>
       <c r="AK2">
-        <v>0.5019618367023974</v>
+        <v>0.542251927126972</v>
       </c>
       <c r="AL2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AM2">
-        <v>155.129</v>
+        <v>152.092</v>
       </c>
       <c r="AN2">
-        <v>-6.075279839271803</v>
+        <v>-8.296209227152513</v>
       </c>
       <c r="AO2">
-        <v>-4.56353591160221</v>
+        <v>-3.6168156424581</v>
       </c>
       <c r="AP2">
-        <v>-5.741849392487811</v>
+        <v>-7.99531925562554</v>
       </c>
       <c r="AQ2">
-        <v>-5.324600816094992</v>
+        <v>-4.256699892170529</v>
       </c>
     </row>
     <row r="3">
@@ -719,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.145</v>
+        <v>-0.106</v>
       </c>
       <c r="G3">
-        <v>0.29375</v>
+        <v>0.1101818181818182</v>
       </c>
       <c r="H3">
-        <v>0.29375</v>
+        <v>0.1101818181818182</v>
       </c>
       <c r="I3">
-        <v>-0.3666666666666667</v>
+        <v>-0.09836363636363636</v>
       </c>
       <c r="J3">
-        <v>-0.3666666666666667</v>
+        <v>-0.09836363636363636</v>
       </c>
       <c r="K3">
-        <v>-20.4</v>
+        <v>-12.2</v>
       </c>
       <c r="L3">
-        <v>-0.425</v>
+        <v>-0.2218181818181818</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>19.6</v>
+        <v>14.7</v>
       </c>
       <c r="V3">
-        <v>0.04021337710299549</v>
+        <v>0.0251067463706234</v>
       </c>
       <c r="W3">
-        <v>-0.1147356580427446</v>
+        <v>-0.08316291751874574</v>
       </c>
       <c r="X3">
-        <v>0.1058969842957786</v>
+        <v>0.1418159487024785</v>
       </c>
       <c r="Y3">
-        <v>-0.2206326423385233</v>
+        <v>-0.2249788662212243</v>
       </c>
       <c r="Z3">
-        <v>0.0988671472708548</v>
+        <v>0.0962379702537183</v>
       </c>
       <c r="AA3">
-        <v>-0.03625128733264676</v>
+        <v>-0.009466316710411201</v>
       </c>
       <c r="AB3">
-        <v>0.06948332823140968</v>
+        <v>0.1059588900182614</v>
       </c>
       <c r="AC3">
-        <v>-0.1057346155640564</v>
+        <v>-0.1154252067286726</v>
       </c>
       <c r="AD3">
-        <v>444.4</v>
+        <v>400.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>444.4</v>
+        <v>400.1</v>
       </c>
       <c r="AG3">
-        <v>424.8</v>
+        <v>385.4</v>
       </c>
       <c r="AH3">
-        <v>0.4769263790512986</v>
+        <v>0.4059456168831169</v>
       </c>
       <c r="AI3">
-        <v>0.7016103568045469</v>
+        <v>0.7156143802539796</v>
       </c>
       <c r="AJ3">
-        <v>0.4656873492655119</v>
+        <v>0.3969512823153775</v>
       </c>
       <c r="AK3">
-        <v>0.6920821114369501</v>
+        <v>0.7079353416605436</v>
       </c>
       <c r="AL3">
-        <v>10.6</v>
+        <v>12.8</v>
       </c>
       <c r="AM3">
-        <v>10.189</v>
+        <v>9.9</v>
       </c>
       <c r="AN3">
-        <v>206.6976744186047</v>
+        <v>24.85093167701863</v>
       </c>
       <c r="AO3">
-        <v>-1.660377358490566</v>
+        <v>-0.42265625</v>
       </c>
       <c r="AP3">
-        <v>197.5813953488372</v>
+        <v>23.93788819875776</v>
       </c>
       <c r="AQ3">
-        <v>-1.727353027775052</v>
+        <v>-0.5464646464646464</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +835,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bangkok Airways Public Company Limited (SET:BA)</t>
+          <t>Airports of Thailand Public Company Limited (SET:AOT)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,25 +844,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.271</v>
+        <v>-0.212</v>
       </c>
       <c r="G4">
-        <v>-0.2989949748743719</v>
+        <v>-0.3466063348416289</v>
       </c>
       <c r="H4">
-        <v>-0.2989949748743719</v>
+        <v>-0.3466063348416289</v>
       </c>
       <c r="I4">
-        <v>-0.4327126833131751</v>
+        <v>-0.6697179984174438</v>
       </c>
       <c r="J4">
-        <v>-0.4327126833131751</v>
+        <v>-0.6697179984174438</v>
       </c>
       <c r="K4">
-        <v>-262</v>
+        <v>-293.8</v>
       </c>
       <c r="L4">
-        <v>-1.64572864321608</v>
+        <v>-0.6647058823529413</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,73 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>32.9</v>
+        <v>100.6</v>
       </c>
       <c r="V4">
-        <v>0.05456958036158567</v>
+        <v>0.00324575809100383</v>
       </c>
       <c r="W4">
-        <v>-0.4398187006882659</v>
+        <v>-0.08792721613694858</v>
       </c>
       <c r="X4">
-        <v>0.1263596512784089</v>
+        <v>0.1082338931101487</v>
       </c>
       <c r="Y4">
-        <v>-0.5661783519666748</v>
+        <v>-0.1961611092470973</v>
       </c>
       <c r="Z4">
-        <v>0.1211623706625345</v>
+        <v>0.08824950324187907</v>
       </c>
       <c r="AA4">
-        <v>-0.05242849452597084</v>
+        <v>-0.05910228067248497</v>
       </c>
       <c r="AB4">
-        <v>0.07205683073158595</v>
+        <v>0.1054734884785369</v>
       </c>
       <c r="AC4">
-        <v>-0.1244853252575568</v>
+        <v>-0.1645757691510219</v>
       </c>
       <c r="AD4">
-        <v>794.5</v>
+        <v>1630.9</v>
       </c>
       <c r="AE4">
-        <v>48.93929591728737</v>
+        <v>14.82677650255084</v>
       </c>
       <c r="AF4">
-        <v>843.4392959172874</v>
+        <v>1645.726776502551</v>
       </c>
       <c r="AG4">
-        <v>810.5392959172874</v>
+        <v>1545.126776502551</v>
       </c>
       <c r="AH4">
-        <v>0.5831545186514254</v>
+        <v>0.05042050938779573</v>
       </c>
       <c r="AI4">
-        <v>0.6847547193736079</v>
+        <v>0.3773021857191097</v>
       </c>
       <c r="AJ4">
-        <v>0.5734517911441448</v>
+        <v>0.04748475709530082</v>
       </c>
       <c r="AK4">
-        <v>0.6761033765556594</v>
+        <v>0.3626013956879175</v>
       </c>
       <c r="AL4">
-        <v>35.1</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="AM4">
-        <v>18.2</v>
+        <v>74.92999999999999</v>
       </c>
       <c r="AN4">
-        <v>-11.11188811188811</v>
+        <v>-11.15145299145299</v>
       </c>
       <c r="AO4">
-        <v>-2.094017094017094</v>
+        <v>-3.865979381443299</v>
       </c>
       <c r="AP4">
-        <v>-11.33621392891311</v>
+        <v>-10.56496941198325</v>
       </c>
       <c r="AQ4">
-        <v>-4.038461538461537</v>
+        <v>-4.003736821032964</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Airports of Thailand Public Company Limited (SET:AOT)</t>
+          <t>Bangkok Airways Public Company Limited (SET:BA)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,118 +972,115 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.322</v>
+        <v>-0.194</v>
       </c>
       <c r="G5">
-        <v>-1.566298342541437</v>
+        <v>-0.4471092077087795</v>
       </c>
       <c r="H5">
-        <v>-1.566298342541437</v>
+        <v>-0.4471092077087795</v>
       </c>
       <c r="I5">
-        <v>-2.307311729361476</v>
+        <v>-0.298462013515327</v>
       </c>
       <c r="J5">
-        <v>-2.307311729361476</v>
+        <v>-0.298462013515327</v>
       </c>
       <c r="K5">
-        <v>-485.5</v>
+        <v>-63.6</v>
       </c>
       <c r="L5">
-        <v>-2.235267034990792</v>
+        <v>-0.2723768736616702</v>
       </c>
       <c r="M5">
-        <v>80.7</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.003088534151839534</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0.1662203913491246</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>80.7</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.003088534151839534</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0.1662203913491246</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>252.2</v>
+        <v>76.3</v>
       </c>
       <c r="V5">
-        <v>0.009652147621981789</v>
+        <v>0.09373464373464373</v>
       </c>
       <c r="W5">
-        <v>-0.107785893479564</v>
+        <v>-0.1635802469135803</v>
       </c>
       <c r="X5">
-        <v>0.07067569176671612</v>
+        <v>0.1680591283481278</v>
       </c>
       <c r="Y5">
-        <v>-0.1784615852462801</v>
+        <v>-0.3316393752617081</v>
       </c>
       <c r="Z5">
-        <v>0.04609467984080613</v>
+        <v>0.1929984301000404</v>
       </c>
       <c r="AA5">
-        <v>-0.106354795457854</v>
+        <v>-0.05760270005295517</v>
       </c>
       <c r="AB5">
-        <v>0.0678704995148784</v>
+        <v>0.1094714216281843</v>
       </c>
       <c r="AC5">
-        <v>-0.1742252949727324</v>
+        <v>-0.1670741216811394</v>
       </c>
       <c r="AD5">
-        <v>1904.5</v>
+        <v>897.7</v>
       </c>
       <c r="AE5">
-        <v>8.040538086563009</v>
+        <v>59.45440077914434</v>
       </c>
       <c r="AF5">
-        <v>1912.540538086563</v>
+        <v>957.1544007791443</v>
       </c>
       <c r="AG5">
-        <v>1660.340538086563</v>
+        <v>880.8544007791444</v>
       </c>
       <c r="AH5">
-        <v>0.06820407587437971</v>
+        <v>0.5404127389221881</v>
       </c>
       <c r="AI5">
-        <v>0.3618165063163719</v>
+        <v>0.6825338874733462</v>
       </c>
       <c r="AJ5">
-        <v>0.05974760396243942</v>
+        <v>0.519722756346625</v>
       </c>
       <c r="AK5">
-        <v>0.3298422963051043</v>
+        <v>0.6642671675170977</v>
       </c>
       <c r="AL5">
-        <v>88.40000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="AM5">
-        <v>81.21000000000001</v>
+        <v>9.799999999999997</v>
       </c>
       <c r="AN5">
-        <v>-5.689490350719962</v>
+        <v>-23.01794871794872</v>
       </c>
       <c r="AO5">
-        <v>-5.712669683257918</v>
+        <v>-2.302631578947369</v>
       </c>
       <c r="AP5">
-        <v>-4.96009003431488</v>
+        <v>-22.58601027638832</v>
       </c>
       <c r="AQ5">
-        <v>-6.218446004186676</v>
+        <v>-7.142857142857145</v>
       </c>
     </row>
     <row r="6">
@@ -1106,25 +1100,25 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.293</v>
+        <v>-0.203</v>
       </c>
       <c r="G6">
-        <v>-1.604692082111437</v>
+        <v>-0.8195105370496261</v>
       </c>
       <c r="H6">
-        <v>-1.604692082111437</v>
+        <v>-0.8195105370496261</v>
       </c>
       <c r="I6">
-        <v>-1.326505702050096</v>
+        <v>-0.917967054216425</v>
       </c>
       <c r="J6">
-        <v>-1.326505702050096</v>
+        <v>-0.917967054216425</v>
       </c>
       <c r="K6">
-        <v>-201.3</v>
+        <v>-321.6</v>
       </c>
       <c r="L6">
-        <v>-1.180645161290323</v>
+        <v>-1.0931339225017</v>
       </c>
       <c r="M6">
         <v>-0</v>
@@ -1148,73 +1142,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.6870000000000001</v>
+        <v>38.6</v>
       </c>
       <c r="V6">
-        <v>0.0009131995214674998</v>
+        <v>0.03584695393759287</v>
       </c>
       <c r="W6">
-        <v>-0.4213941804479799</v>
+        <v>-1.236447520184544</v>
       </c>
       <c r="X6">
-        <v>0.1405238188551625</v>
+        <v>0.1701501837797212</v>
       </c>
       <c r="Y6">
-        <v>-0.5619179993031425</v>
+        <v>-1.406597703964266</v>
       </c>
       <c r="Z6">
-        <v>0.1213396946164827</v>
+        <v>0.2261437317088832</v>
       </c>
       <c r="AA6">
-        <v>-0.1609577967937816</v>
+        <v>-0.2075924952263131</v>
       </c>
       <c r="AB6">
-        <v>0.07244935512407305</v>
+        <v>0.1061535958270697</v>
       </c>
       <c r="AC6">
-        <v>-0.2334071519178546</v>
+        <v>-0.3137460910533828</v>
       </c>
       <c r="AD6">
-        <v>1301.7</v>
+        <v>1306.1</v>
       </c>
       <c r="AE6">
-        <v>4.446110997706549</v>
+        <v>2.329536752361121</v>
       </c>
       <c r="AF6">
-        <v>1306.146110997707</v>
+        <v>1308.429536752361</v>
       </c>
       <c r="AG6">
-        <v>1305.459110997707</v>
+        <v>1269.829536752361</v>
       </c>
       <c r="AH6">
-        <v>0.6345301458315232</v>
+        <v>0.5485549782910493</v>
       </c>
       <c r="AI6">
-        <v>0.8571940571795642</v>
+        <v>0.912860234302435</v>
       </c>
       <c r="AJ6">
-        <v>0.6344081306799577</v>
+        <v>0.541129103194428</v>
       </c>
       <c r="AK6">
-        <v>0.8571296422911273</v>
+        <v>0.910448587551368</v>
       </c>
       <c r="AL6">
-        <v>46.9</v>
+        <v>58.2</v>
       </c>
       <c r="AM6">
-        <v>45.53</v>
+        <v>57.462</v>
       </c>
       <c r="AN6">
-        <v>-3.973685817204958</v>
+        <v>-3.826838558452974</v>
       </c>
       <c r="AO6">
-        <v>-4.901918976545843</v>
+        <v>-4.673539518900343</v>
       </c>
       <c r="AP6">
-        <v>-3.985161215573926</v>
+        <v>-3.7205670575809</v>
       </c>
       <c r="AQ6">
-        <v>-5.049417966176148</v>
+        <v>-4.733563050363719</v>
       </c>
     </row>
   </sheetData>
